--- a/files/temp_files/statement_2025_04.xlsx
+++ b/files/temp_files/statement_2025_04.xlsx
@@ -594,7 +594,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>34.01</v>
+        <v>-34.01</v>
       </c>
       <c r="D2" t="s">
         <v>58</v>
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>271.03</v>
+        <v>-271.03</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -622,7 +622,7 @@
         <v>36</v>
       </c>
       <c r="C4">
-        <v>15.61</v>
+        <v>-15.61</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -650,7 +650,7 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>15.61</v>
+        <v>-15.61</v>
       </c>
       <c r="D6" t="s">
         <v>62</v>
@@ -678,7 +678,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>91.56</v>
+        <v>-91.56</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C9">
-        <v>54.48</v>
+        <v>-54.48</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
@@ -706,7 +706,7 @@
         <v>42</v>
       </c>
       <c r="C10">
-        <v>141.18</v>
+        <v>-141.18</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C12">
-        <v>213.7</v>
+        <v>-213.7</v>
       </c>
       <c r="D12" t="s">
         <v>63</v>
@@ -748,7 +748,7 @@
         <v>40</v>
       </c>
       <c r="C13">
-        <v>36.29</v>
+        <v>-36.29</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
@@ -762,7 +762,7 @@
         <v>45</v>
       </c>
       <c r="C14">
-        <v>874.6</v>
+        <v>-874.6</v>
       </c>
       <c r="D14" t="s">
         <v>64</v>
@@ -776,7 +776,7 @@
         <v>38</v>
       </c>
       <c r="C15">
-        <v>12.65</v>
+        <v>-12.65</v>
       </c>
       <c r="D15" t="s">
         <v>62</v>
@@ -790,7 +790,7 @@
         <v>46</v>
       </c>
       <c r="C16">
-        <v>791.26</v>
+        <v>-791.26</v>
       </c>
       <c r="D16" t="s">
         <v>64</v>
@@ -804,7 +804,7 @@
         <v>34</v>
       </c>
       <c r="C17">
-        <v>120.07</v>
+        <v>-120.07</v>
       </c>
       <c r="D17" t="s">
         <v>58</v>
@@ -832,7 +832,7 @@
         <v>45</v>
       </c>
       <c r="C19">
-        <v>855.42</v>
+        <v>-855.42</v>
       </c>
       <c r="D19" t="s">
         <v>64</v>
@@ -846,7 +846,7 @@
         <v>45</v>
       </c>
       <c r="C20">
-        <v>773.54</v>
+        <v>-773.54</v>
       </c>
       <c r="D20" t="s">
         <v>64</v>
@@ -860,7 +860,7 @@
         <v>42</v>
       </c>
       <c r="C21">
-        <v>12.52</v>
+        <v>-12.52</v>
       </c>
       <c r="D21" t="s">
         <v>58</v>
@@ -874,7 +874,7 @@
         <v>42</v>
       </c>
       <c r="C22">
-        <v>148.33</v>
+        <v>-148.33</v>
       </c>
       <c r="D22" t="s">
         <v>58</v>
@@ -888,7 +888,7 @@
         <v>46</v>
       </c>
       <c r="C23">
-        <v>56.02</v>
+        <v>-56.02</v>
       </c>
       <c r="D23" t="s">
         <v>64</v>
@@ -902,7 +902,7 @@
         <v>44</v>
       </c>
       <c r="C24">
-        <v>63.83</v>
+        <v>-63.83</v>
       </c>
       <c r="D24" t="s">
         <v>63</v>
@@ -916,7 +916,7 @@
         <v>36</v>
       </c>
       <c r="C25">
-        <v>51.77</v>
+        <v>-51.77</v>
       </c>
       <c r="D25" t="s">
         <v>60</v>
@@ -930,7 +930,7 @@
         <v>41</v>
       </c>
       <c r="C26">
-        <v>156.83</v>
+        <v>-156.83</v>
       </c>
       <c r="D26" t="s">
         <v>58</v>
@@ -944,7 +944,7 @@
         <v>47</v>
       </c>
       <c r="C27">
-        <v>148.07</v>
+        <v>-148.07</v>
       </c>
       <c r="D27" t="s">
         <v>65</v>
@@ -958,7 +958,7 @@
         <v>46</v>
       </c>
       <c r="C28">
-        <v>275.62</v>
+        <v>-275.62</v>
       </c>
       <c r="D28" t="s">
         <v>64</v>
@@ -972,7 +972,7 @@
         <v>35</v>
       </c>
       <c r="C29">
-        <v>33.58</v>
+        <v>-33.58</v>
       </c>
       <c r="D29" t="s">
         <v>59</v>
@@ -1000,7 +1000,7 @@
         <v>47</v>
       </c>
       <c r="C31">
-        <v>127.71</v>
+        <v>-127.71</v>
       </c>
       <c r="D31" t="s">
         <v>65</v>
@@ -1014,7 +1014,7 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>19.44</v>
+        <v>-19.44</v>
       </c>
       <c r="D32" t="s">
         <v>60</v>
@@ -1028,7 +1028,7 @@
         <v>46</v>
       </c>
       <c r="C33">
-        <v>777.6900000000001</v>
+        <v>-777.6900000000001</v>
       </c>
       <c r="D33" t="s">
         <v>64</v>
@@ -1042,7 +1042,7 @@
         <v>48</v>
       </c>
       <c r="C34">
-        <v>22.89</v>
+        <v>-22.89</v>
       </c>
       <c r="D34" t="s">
         <v>65</v>
@@ -1070,7 +1070,7 @@
         <v>49</v>
       </c>
       <c r="C36">
-        <v>32.43</v>
+        <v>-32.43</v>
       </c>
       <c r="D36" t="s">
         <v>60</v>
@@ -1084,7 +1084,7 @@
         <v>35</v>
       </c>
       <c r="C37">
-        <v>262.7</v>
+        <v>-262.7</v>
       </c>
       <c r="D37" t="s">
         <v>59</v>
@@ -1112,7 +1112,7 @@
         <v>50</v>
       </c>
       <c r="C39">
-        <v>117.01</v>
+        <v>-117.01</v>
       </c>
       <c r="D39" t="s">
         <v>63</v>
@@ -1140,7 +1140,7 @@
         <v>41</v>
       </c>
       <c r="C41">
-        <v>193.19</v>
+        <v>-193.19</v>
       </c>
       <c r="D41" t="s">
         <v>58</v>
@@ -1168,7 +1168,7 @@
         <v>51</v>
       </c>
       <c r="C43">
-        <v>88.95999999999999</v>
+        <v>-88.95999999999999</v>
       </c>
       <c r="D43" t="s">
         <v>59</v>
@@ -1182,7 +1182,7 @@
         <v>35</v>
       </c>
       <c r="C44">
-        <v>136.66</v>
+        <v>-136.66</v>
       </c>
       <c r="D44" t="s">
         <v>59</v>
@@ -1196,7 +1196,7 @@
         <v>46</v>
       </c>
       <c r="C45">
-        <v>581.36</v>
+        <v>-581.36</v>
       </c>
       <c r="D45" t="s">
         <v>64</v>
@@ -1224,7 +1224,7 @@
         <v>36</v>
       </c>
       <c r="C47">
-        <v>93.70999999999999</v>
+        <v>-93.70999999999999</v>
       </c>
       <c r="D47" t="s">
         <v>60</v>
@@ -1238,7 +1238,7 @@
         <v>47</v>
       </c>
       <c r="C48">
-        <v>30.99</v>
+        <v>-30.99</v>
       </c>
       <c r="D48" t="s">
         <v>65</v>
@@ -1252,7 +1252,7 @@
         <v>45</v>
       </c>
       <c r="C49">
-        <v>167.85</v>
+        <v>-167.85</v>
       </c>
       <c r="D49" t="s">
         <v>64</v>
@@ -1266,7 +1266,7 @@
         <v>46</v>
       </c>
       <c r="C50">
-        <v>389.04</v>
+        <v>-389.04</v>
       </c>
       <c r="D50" t="s">
         <v>64</v>
@@ -1280,7 +1280,7 @@
         <v>35</v>
       </c>
       <c r="C51">
-        <v>451.34</v>
+        <v>-451.34</v>
       </c>
       <c r="D51" t="s">
         <v>59</v>
@@ -1294,7 +1294,7 @@
         <v>52</v>
       </c>
       <c r="C52">
-        <v>225.02</v>
+        <v>-225.02</v>
       </c>
       <c r="D52" t="s">
         <v>59</v>
@@ -1308,7 +1308,7 @@
         <v>45</v>
       </c>
       <c r="C53">
-        <v>236.49</v>
+        <v>-236.49</v>
       </c>
       <c r="D53" t="s">
         <v>64</v>
@@ -1322,7 +1322,7 @@
         <v>45</v>
       </c>
       <c r="C54">
-        <v>650.55</v>
+        <v>-650.55</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
@@ -1336,7 +1336,7 @@
         <v>53</v>
       </c>
       <c r="C55">
-        <v>116.47</v>
+        <v>-116.47</v>
       </c>
       <c r="D55" t="s">
         <v>64</v>
@@ -1350,7 +1350,7 @@
         <v>41</v>
       </c>
       <c r="C56">
-        <v>117.89</v>
+        <v>-117.89</v>
       </c>
       <c r="D56" t="s">
         <v>58</v>
@@ -1364,7 +1364,7 @@
         <v>34</v>
       </c>
       <c r="C57">
-        <v>44.08</v>
+        <v>-44.08</v>
       </c>
       <c r="D57" t="s">
         <v>58</v>
@@ -1378,7 +1378,7 @@
         <v>38</v>
       </c>
       <c r="C58">
-        <v>44.72</v>
+        <v>-44.72</v>
       </c>
       <c r="D58" t="s">
         <v>62</v>
@@ -1392,7 +1392,7 @@
         <v>40</v>
       </c>
       <c r="C59">
-        <v>17.35</v>
+        <v>-17.35</v>
       </c>
       <c r="D59" t="s">
         <v>60</v>
@@ -1406,7 +1406,7 @@
         <v>54</v>
       </c>
       <c r="C60">
-        <v>50.76</v>
+        <v>-50.76</v>
       </c>
       <c r="D60" t="s">
         <v>65</v>
@@ -1420,7 +1420,7 @@
         <v>51</v>
       </c>
       <c r="C61">
-        <v>13.62</v>
+        <v>-13.62</v>
       </c>
       <c r="D61" t="s">
         <v>59</v>
@@ -1434,7 +1434,7 @@
         <v>51</v>
       </c>
       <c r="C62">
-        <v>478.98</v>
+        <v>-478.98</v>
       </c>
       <c r="D62" t="s">
         <v>59</v>
@@ -1462,7 +1462,7 @@
         <v>35</v>
       </c>
       <c r="C64">
-        <v>392.84</v>
+        <v>-392.84</v>
       </c>
       <c r="D64" t="s">
         <v>59</v>
@@ -1476,7 +1476,7 @@
         <v>34</v>
       </c>
       <c r="C65">
-        <v>151.8</v>
+        <v>-151.8</v>
       </c>
       <c r="D65" t="s">
         <v>58</v>
@@ -1490,7 +1490,7 @@
         <v>38</v>
       </c>
       <c r="C66">
-        <v>24.34</v>
+        <v>-24.34</v>
       </c>
       <c r="D66" t="s">
         <v>62</v>
@@ -1504,7 +1504,7 @@
         <v>51</v>
       </c>
       <c r="C67">
-        <v>161.51</v>
+        <v>-161.51</v>
       </c>
       <c r="D67" t="s">
         <v>59</v>
@@ -1518,7 +1518,7 @@
         <v>46</v>
       </c>
       <c r="C68">
-        <v>722.71</v>
+        <v>-722.71</v>
       </c>
       <c r="D68" t="s">
         <v>64</v>
@@ -1532,7 +1532,7 @@
         <v>44</v>
       </c>
       <c r="C69">
-        <v>113.58</v>
+        <v>-113.58</v>
       </c>
       <c r="D69" t="s">
         <v>63</v>
@@ -1546,7 +1546,7 @@
         <v>42</v>
       </c>
       <c r="C70">
-        <v>15.24</v>
+        <v>-15.24</v>
       </c>
       <c r="D70" t="s">
         <v>58</v>
@@ -1560,7 +1560,7 @@
         <v>51</v>
       </c>
       <c r="C71">
-        <v>325.65</v>
+        <v>-325.65</v>
       </c>
       <c r="D71" t="s">
         <v>59</v>
@@ -1574,7 +1574,7 @@
         <v>52</v>
       </c>
       <c r="C72">
-        <v>399.71</v>
+        <v>-399.71</v>
       </c>
       <c r="D72" t="s">
         <v>59</v>
@@ -1588,7 +1588,7 @@
         <v>34</v>
       </c>
       <c r="C73">
-        <v>43.3</v>
+        <v>-43.3</v>
       </c>
       <c r="D73" t="s">
         <v>58</v>
@@ -1602,7 +1602,7 @@
         <v>50</v>
       </c>
       <c r="C74">
-        <v>244.22</v>
+        <v>-244.22</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
@@ -1616,7 +1616,7 @@
         <v>48</v>
       </c>
       <c r="C75">
-        <v>74.40000000000001</v>
+        <v>-74.40000000000001</v>
       </c>
       <c r="D75" t="s">
         <v>65</v>
@@ -1630,7 +1630,7 @@
         <v>38</v>
       </c>
       <c r="C76">
-        <v>8.58</v>
+        <v>-8.58</v>
       </c>
       <c r="D76" t="s">
         <v>62</v>
@@ -1644,7 +1644,7 @@
         <v>54</v>
       </c>
       <c r="C77">
-        <v>132.22</v>
+        <v>-132.22</v>
       </c>
       <c r="D77" t="s">
         <v>65</v>
@@ -1658,7 +1658,7 @@
         <v>40</v>
       </c>
       <c r="C78">
-        <v>18.91</v>
+        <v>-18.91</v>
       </c>
       <c r="D78" t="s">
         <v>60</v>
@@ -1672,7 +1672,7 @@
         <v>42</v>
       </c>
       <c r="C79">
-        <v>131.84</v>
+        <v>-131.84</v>
       </c>
       <c r="D79" t="s">
         <v>58</v>
@@ -1686,7 +1686,7 @@
         <v>55</v>
       </c>
       <c r="C80">
-        <v>36.31</v>
+        <v>-36.31</v>
       </c>
       <c r="D80" t="s">
         <v>62</v>
@@ -1700,7 +1700,7 @@
         <v>41</v>
       </c>
       <c r="C81">
-        <v>179.21</v>
+        <v>-179.21</v>
       </c>
       <c r="D81" t="s">
         <v>58</v>
@@ -1714,7 +1714,7 @@
         <v>56</v>
       </c>
       <c r="C82">
-        <v>292.67</v>
+        <v>-292.67</v>
       </c>
       <c r="D82" t="s">
         <v>63</v>
@@ -1728,7 +1728,7 @@
         <v>52</v>
       </c>
       <c r="C83">
-        <v>173.83</v>
+        <v>-173.83</v>
       </c>
       <c r="D83" t="s">
         <v>59</v>
@@ -1742,7 +1742,7 @@
         <v>47</v>
       </c>
       <c r="C84">
-        <v>83.97</v>
+        <v>-83.97</v>
       </c>
       <c r="D84" t="s">
         <v>65</v>
@@ -1756,7 +1756,7 @@
         <v>49</v>
       </c>
       <c r="C85">
-        <v>37.46</v>
+        <v>-37.46</v>
       </c>
       <c r="D85" t="s">
         <v>60</v>
@@ -1770,7 +1770,7 @@
         <v>45</v>
       </c>
       <c r="C86">
-        <v>748.5700000000001</v>
+        <v>-748.5700000000001</v>
       </c>
       <c r="D86" t="s">
         <v>64</v>
@@ -1784,7 +1784,7 @@
         <v>42</v>
       </c>
       <c r="C87">
-        <v>58.95</v>
+        <v>-58.95</v>
       </c>
       <c r="D87" t="s">
         <v>58</v>
@@ -1812,7 +1812,7 @@
         <v>52</v>
       </c>
       <c r="C89">
-        <v>438.05</v>
+        <v>-438.05</v>
       </c>
       <c r="D89" t="s">
         <v>59</v>
@@ -1826,7 +1826,7 @@
         <v>41</v>
       </c>
       <c r="C90">
-        <v>161.49</v>
+        <v>-161.49</v>
       </c>
       <c r="D90" t="s">
         <v>58</v>
@@ -1840,7 +1840,7 @@
         <v>42</v>
       </c>
       <c r="C91">
-        <v>33.43</v>
+        <v>-33.43</v>
       </c>
       <c r="D91" t="s">
         <v>58</v>
@@ -1854,7 +1854,7 @@
         <v>49</v>
       </c>
       <c r="C92">
-        <v>13.22</v>
+        <v>-13.22</v>
       </c>
       <c r="D92" t="s">
         <v>60</v>
@@ -1868,7 +1868,7 @@
         <v>34</v>
       </c>
       <c r="C93">
-        <v>38.09</v>
+        <v>-38.09</v>
       </c>
       <c r="D93" t="s">
         <v>58</v>
@@ -1882,7 +1882,7 @@
         <v>55</v>
       </c>
       <c r="C94">
-        <v>1.29</v>
+        <v>-1.29</v>
       </c>
       <c r="D94" t="s">
         <v>62</v>
@@ -1896,7 +1896,7 @@
         <v>49</v>
       </c>
       <c r="C95">
-        <v>83.69</v>
+        <v>-83.69</v>
       </c>
       <c r="D95" t="s">
         <v>60</v>
@@ -1910,7 +1910,7 @@
         <v>49</v>
       </c>
       <c r="C96">
-        <v>78.29000000000001</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="D96" t="s">
         <v>60</v>
@@ -1952,7 +1952,7 @@
         <v>54</v>
       </c>
       <c r="C99">
-        <v>24.96</v>
+        <v>-24.96</v>
       </c>
       <c r="D99" t="s">
         <v>65</v>
@@ -1980,7 +1980,7 @@
         <v>50</v>
       </c>
       <c r="C101">
-        <v>196.88</v>
+        <v>-196.88</v>
       </c>
       <c r="D101" t="s">
         <v>63</v>
@@ -1994,7 +1994,7 @@
         <v>35</v>
       </c>
       <c r="C102">
-        <v>62.99</v>
+        <v>-62.99</v>
       </c>
       <c r="D102" t="s">
         <v>59</v>
@@ -2008,7 +2008,7 @@
         <v>36</v>
       </c>
       <c r="C103">
-        <v>94.92</v>
+        <v>-94.92</v>
       </c>
       <c r="D103" t="s">
         <v>60</v>
@@ -2022,7 +2022,7 @@
         <v>49</v>
       </c>
       <c r="C104">
-        <v>58.57</v>
+        <v>-58.57</v>
       </c>
       <c r="D104" t="s">
         <v>60</v>
@@ -2036,7 +2036,7 @@
         <v>56</v>
       </c>
       <c r="C105">
-        <v>100.18</v>
+        <v>-100.18</v>
       </c>
       <c r="D105" t="s">
         <v>63</v>
@@ -2064,7 +2064,7 @@
         <v>54</v>
       </c>
       <c r="C107">
-        <v>93.83</v>
+        <v>-93.83</v>
       </c>
       <c r="D107" t="s">
         <v>65</v>
@@ -2078,7 +2078,7 @@
         <v>48</v>
       </c>
       <c r="C108">
-        <v>141.79</v>
+        <v>-141.79</v>
       </c>
       <c r="D108" t="s">
         <v>65</v>
@@ -2092,7 +2092,7 @@
         <v>56</v>
       </c>
       <c r="C109">
-        <v>163.92</v>
+        <v>-163.92</v>
       </c>
       <c r="D109" t="s">
         <v>63</v>
@@ -2106,7 +2106,7 @@
         <v>55</v>
       </c>
       <c r="C110">
-        <v>15.74</v>
+        <v>-15.74</v>
       </c>
       <c r="D110" t="s">
         <v>62</v>
@@ -2120,7 +2120,7 @@
         <v>51</v>
       </c>
       <c r="C111">
-        <v>189.19</v>
+        <v>-189.19</v>
       </c>
       <c r="D111" t="s">
         <v>59</v>
@@ -2162,7 +2162,7 @@
         <v>45</v>
       </c>
       <c r="C114">
-        <v>366.59</v>
+        <v>-366.59</v>
       </c>
       <c r="D114" t="s">
         <v>64</v>
@@ -2176,7 +2176,7 @@
         <v>50</v>
       </c>
       <c r="C115">
-        <v>166.32</v>
+        <v>-166.32</v>
       </c>
       <c r="D115" t="s">
         <v>63</v>
@@ -2190,7 +2190,7 @@
         <v>38</v>
       </c>
       <c r="C116">
-        <v>49.31</v>
+        <v>-49.31</v>
       </c>
       <c r="D116" t="s">
         <v>62</v>
@@ -2204,7 +2204,7 @@
         <v>51</v>
       </c>
       <c r="C117">
-        <v>168.33</v>
+        <v>-168.33</v>
       </c>
       <c r="D117" t="s">
         <v>59</v>
@@ -2232,7 +2232,7 @@
         <v>45</v>
       </c>
       <c r="C119">
-        <v>883.54</v>
+        <v>-883.54</v>
       </c>
       <c r="D119" t="s">
         <v>64</v>
@@ -2246,7 +2246,7 @@
         <v>36</v>
       </c>
       <c r="C120">
-        <v>19.6</v>
+        <v>-19.6</v>
       </c>
       <c r="D120" t="s">
         <v>60</v>
@@ -2260,7 +2260,7 @@
         <v>49</v>
       </c>
       <c r="C121">
-        <v>51.24</v>
+        <v>-51.24</v>
       </c>
       <c r="D121" t="s">
         <v>60</v>
@@ -2274,7 +2274,7 @@
         <v>55</v>
       </c>
       <c r="C122">
-        <v>45.95</v>
+        <v>-45.95</v>
       </c>
       <c r="D122" t="s">
         <v>62</v>
@@ -2302,7 +2302,7 @@
         <v>44</v>
       </c>
       <c r="C124">
-        <v>223.93</v>
+        <v>-223.93</v>
       </c>
       <c r="D124" t="s">
         <v>63</v>
@@ -2316,7 +2316,7 @@
         <v>50</v>
       </c>
       <c r="C125">
-        <v>174.58</v>
+        <v>-174.58</v>
       </c>
       <c r="D125" t="s">
         <v>63</v>
@@ -2344,7 +2344,7 @@
         <v>40</v>
       </c>
       <c r="C127">
-        <v>95.98999999999999</v>
+        <v>-95.98999999999999</v>
       </c>
       <c r="D127" t="s">
         <v>60</v>
@@ -2358,7 +2358,7 @@
         <v>52</v>
       </c>
       <c r="C128">
-        <v>123.61</v>
+        <v>-123.61</v>
       </c>
       <c r="D128" t="s">
         <v>59</v>
@@ -2372,7 +2372,7 @@
         <v>49</v>
       </c>
       <c r="C129">
-        <v>12.4</v>
+        <v>-12.4</v>
       </c>
       <c r="D129" t="s">
         <v>60</v>
@@ -2386,7 +2386,7 @@
         <v>35</v>
       </c>
       <c r="C130">
-        <v>441.78</v>
+        <v>-441.78</v>
       </c>
       <c r="D130" t="s">
         <v>59</v>
@@ -2414,7 +2414,7 @@
         <v>52</v>
       </c>
       <c r="C132">
-        <v>262.65</v>
+        <v>-262.65</v>
       </c>
       <c r="D132" t="s">
         <v>59</v>
@@ -2428,7 +2428,7 @@
         <v>40</v>
       </c>
       <c r="C133">
-        <v>23.11</v>
+        <v>-23.11</v>
       </c>
       <c r="D133" t="s">
         <v>60</v>
@@ -2442,7 +2442,7 @@
         <v>54</v>
       </c>
       <c r="C134">
-        <v>149.26</v>
+        <v>-149.26</v>
       </c>
       <c r="D134" t="s">
         <v>65</v>
@@ -2456,7 +2456,7 @@
         <v>45</v>
       </c>
       <c r="C135">
-        <v>27.45</v>
+        <v>-27.45</v>
       </c>
       <c r="D135" t="s">
         <v>64</v>
@@ -2470,7 +2470,7 @@
         <v>34</v>
       </c>
       <c r="C136">
-        <v>135.5</v>
+        <v>-135.5</v>
       </c>
       <c r="D136" t="s">
         <v>58</v>
@@ -2484,7 +2484,7 @@
         <v>46</v>
       </c>
       <c r="C137">
-        <v>551.12</v>
+        <v>-551.12</v>
       </c>
       <c r="D137" t="s">
         <v>64</v>
@@ -2498,7 +2498,7 @@
         <v>48</v>
       </c>
       <c r="C138">
-        <v>144.95</v>
+        <v>-144.95</v>
       </c>
       <c r="D138" t="s">
         <v>65</v>
@@ -2526,7 +2526,7 @@
         <v>55</v>
       </c>
       <c r="C140">
-        <v>16.43</v>
+        <v>-16.43</v>
       </c>
       <c r="D140" t="s">
         <v>62</v>
@@ -2540,7 +2540,7 @@
         <v>52</v>
       </c>
       <c r="C141">
-        <v>25.9</v>
+        <v>-25.9</v>
       </c>
       <c r="D141" t="s">
         <v>59</v>
@@ -2554,7 +2554,7 @@
         <v>48</v>
       </c>
       <c r="C142">
-        <v>108.46</v>
+        <v>-108.46</v>
       </c>
       <c r="D142" t="s">
         <v>65</v>
@@ -2568,7 +2568,7 @@
         <v>50</v>
       </c>
       <c r="C143">
-        <v>36.13</v>
+        <v>-36.13</v>
       </c>
       <c r="D143" t="s">
         <v>63</v>
@@ -2624,7 +2624,7 @@
         <v>53</v>
       </c>
       <c r="C147">
-        <v>259.82</v>
+        <v>-259.82</v>
       </c>
       <c r="D147" t="s">
         <v>64</v>
@@ -2638,7 +2638,7 @@
         <v>52</v>
       </c>
       <c r="C148">
-        <v>171.55</v>
+        <v>-171.55</v>
       </c>
       <c r="D148" t="s">
         <v>59</v>
@@ -2652,7 +2652,7 @@
         <v>40</v>
       </c>
       <c r="C149">
-        <v>70.92</v>
+        <v>-70.92</v>
       </c>
       <c r="D149" t="s">
         <v>60</v>
@@ -2666,7 +2666,7 @@
         <v>49</v>
       </c>
       <c r="C150">
-        <v>56.93</v>
+        <v>-56.93</v>
       </c>
       <c r="D150" t="s">
         <v>60</v>
@@ -2680,7 +2680,7 @@
         <v>57</v>
       </c>
       <c r="C151">
-        <v>12.51</v>
+        <v>-12.51</v>
       </c>
       <c r="D151" t="s">
         <v>62</v>
@@ -2694,7 +2694,7 @@
         <v>56</v>
       </c>
       <c r="C152">
-        <v>203.25</v>
+        <v>-203.25</v>
       </c>
       <c r="D152" t="s">
         <v>63</v>
@@ -2708,7 +2708,7 @@
         <v>38</v>
       </c>
       <c r="C153">
-        <v>31.69</v>
+        <v>-31.69</v>
       </c>
       <c r="D153" t="s">
         <v>62</v>
@@ -2722,7 +2722,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>231.67</v>
+        <v>-231.67</v>
       </c>
       <c r="D154" t="s">
         <v>63</v>
@@ -2750,7 +2750,7 @@
         <v>38</v>
       </c>
       <c r="C156">
-        <v>35.96</v>
+        <v>-35.96</v>
       </c>
       <c r="D156" t="s">
         <v>62</v>
@@ -2764,7 +2764,7 @@
         <v>41</v>
       </c>
       <c r="C157">
-        <v>177.1</v>
+        <v>-177.1</v>
       </c>
       <c r="D157" t="s">
         <v>58</v>
@@ -2792,7 +2792,7 @@
         <v>41</v>
       </c>
       <c r="C159">
-        <v>185.51</v>
+        <v>-185.51</v>
       </c>
       <c r="D159" t="s">
         <v>58</v>
@@ -2806,7 +2806,7 @@
         <v>41</v>
       </c>
       <c r="C160">
-        <v>24.1</v>
+        <v>-24.1</v>
       </c>
       <c r="D160" t="s">
         <v>58</v>
@@ -2820,7 +2820,7 @@
         <v>38</v>
       </c>
       <c r="C161">
-        <v>26.76</v>
+        <v>-26.76</v>
       </c>
       <c r="D161" t="s">
         <v>62</v>
@@ -2834,7 +2834,7 @@
         <v>56</v>
       </c>
       <c r="C162">
-        <v>185.68</v>
+        <v>-185.68</v>
       </c>
       <c r="D162" t="s">
         <v>63</v>
@@ -2848,7 +2848,7 @@
         <v>34</v>
       </c>
       <c r="C163">
-        <v>115.46</v>
+        <v>-115.46</v>
       </c>
       <c r="D163" t="s">
         <v>58</v>
@@ -2862,7 +2862,7 @@
         <v>57</v>
       </c>
       <c r="C164">
-        <v>15.71</v>
+        <v>-15.71</v>
       </c>
       <c r="D164" t="s">
         <v>62</v>
@@ -2876,7 +2876,7 @@
         <v>42</v>
       </c>
       <c r="C165">
-        <v>70.12</v>
+        <v>-70.12</v>
       </c>
       <c r="D165" t="s">
         <v>58</v>
@@ -2904,7 +2904,7 @@
         <v>40</v>
       </c>
       <c r="C167">
-        <v>74.11</v>
+        <v>-74.11</v>
       </c>
       <c r="D167" t="s">
         <v>60</v>
@@ -2918,7 +2918,7 @@
         <v>48</v>
       </c>
       <c r="C168">
-        <v>144.69</v>
+        <v>-144.69</v>
       </c>
       <c r="D168" t="s">
         <v>65</v>
@@ -2932,7 +2932,7 @@
         <v>48</v>
       </c>
       <c r="C169">
-        <v>148.83</v>
+        <v>-148.83</v>
       </c>
       <c r="D169" t="s">
         <v>65</v>
@@ -2946,7 +2946,7 @@
         <v>53</v>
       </c>
       <c r="C170">
-        <v>417.93</v>
+        <v>-417.93</v>
       </c>
       <c r="D170" t="s">
         <v>64</v>
@@ -2960,7 +2960,7 @@
         <v>53</v>
       </c>
       <c r="C171">
-        <v>138.36</v>
+        <v>-138.36</v>
       </c>
       <c r="D171" t="s">
         <v>64</v>
@@ -2974,7 +2974,7 @@
         <v>36</v>
       </c>
       <c r="C172">
-        <v>12.48</v>
+        <v>-12.48</v>
       </c>
       <c r="D172" t="s">
         <v>60</v>
@@ -3002,7 +3002,7 @@
         <v>38</v>
       </c>
       <c r="C174">
-        <v>24.52</v>
+        <v>-24.52</v>
       </c>
       <c r="D174" t="s">
         <v>62</v>
@@ -3016,7 +3016,7 @@
         <v>48</v>
       </c>
       <c r="C175">
-        <v>80.23</v>
+        <v>-80.23</v>
       </c>
       <c r="D175" t="s">
         <v>65</v>
@@ -3030,7 +3030,7 @@
         <v>35</v>
       </c>
       <c r="C176">
-        <v>288.12</v>
+        <v>-288.12</v>
       </c>
       <c r="D176" t="s">
         <v>59</v>
@@ -3044,7 +3044,7 @@
         <v>53</v>
       </c>
       <c r="C177">
-        <v>211.38</v>
+        <v>-211.38</v>
       </c>
       <c r="D177" t="s">
         <v>64</v>
@@ -3058,7 +3058,7 @@
         <v>44</v>
       </c>
       <c r="C178">
-        <v>274.24</v>
+        <v>-274.24</v>
       </c>
       <c r="D178" t="s">
         <v>63</v>
@@ -3072,7 +3072,7 @@
         <v>56</v>
       </c>
       <c r="C179">
-        <v>166.19</v>
+        <v>-166.19</v>
       </c>
       <c r="D179" t="s">
         <v>63</v>
@@ -3086,7 +3086,7 @@
         <v>47</v>
       </c>
       <c r="C180">
-        <v>84.56999999999999</v>
+        <v>-84.56999999999999</v>
       </c>
       <c r="D180" t="s">
         <v>65</v>
@@ -3100,7 +3100,7 @@
         <v>51</v>
       </c>
       <c r="C181">
-        <v>18.31</v>
+        <v>-18.31</v>
       </c>
       <c r="D181" t="s">
         <v>59</v>
@@ -3128,7 +3128,7 @@
         <v>57</v>
       </c>
       <c r="C183">
-        <v>25.62</v>
+        <v>-25.62</v>
       </c>
       <c r="D183" t="s">
         <v>62</v>
@@ -3156,7 +3156,7 @@
         <v>34</v>
       </c>
       <c r="C185">
-        <v>69.5</v>
+        <v>-69.5</v>
       </c>
       <c r="D185" t="s">
         <v>58</v>
@@ -3170,7 +3170,7 @@
         <v>57</v>
       </c>
       <c r="C186">
-        <v>47.75</v>
+        <v>-47.75</v>
       </c>
       <c r="D186" t="s">
         <v>62</v>
@@ -3184,7 +3184,7 @@
         <v>45</v>
       </c>
       <c r="C187">
-        <v>389.02</v>
+        <v>-389.02</v>
       </c>
       <c r="D187" t="s">
         <v>64</v>
@@ -3198,7 +3198,7 @@
         <v>35</v>
       </c>
       <c r="C188">
-        <v>5.61</v>
+        <v>-5.61</v>
       </c>
       <c r="D188" t="s">
         <v>59</v>
@@ -3212,7 +3212,7 @@
         <v>47</v>
       </c>
       <c r="C189">
-        <v>37.08</v>
+        <v>-37.08</v>
       </c>
       <c r="D189" t="s">
         <v>65</v>
@@ -3226,7 +3226,7 @@
         <v>46</v>
       </c>
       <c r="C190">
-        <v>882.24</v>
+        <v>-882.24</v>
       </c>
       <c r="D190" t="s">
         <v>64</v>
@@ -3240,7 +3240,7 @@
         <v>36</v>
       </c>
       <c r="C191">
-        <v>30.21</v>
+        <v>-30.21</v>
       </c>
       <c r="D191" t="s">
         <v>60</v>
@@ -3254,7 +3254,7 @@
         <v>54</v>
       </c>
       <c r="C192">
-        <v>100.28</v>
+        <v>-100.28</v>
       </c>
       <c r="D192" t="s">
         <v>65</v>
@@ -3268,7 +3268,7 @@
         <v>45</v>
       </c>
       <c r="C193">
-        <v>90.42</v>
+        <v>-90.42</v>
       </c>
       <c r="D193" t="s">
         <v>64</v>
@@ -3282,7 +3282,7 @@
         <v>44</v>
       </c>
       <c r="C194">
-        <v>98.94</v>
+        <v>-98.94</v>
       </c>
       <c r="D194" t="s">
         <v>63</v>
@@ -3296,7 +3296,7 @@
         <v>53</v>
       </c>
       <c r="C195">
-        <v>574.16</v>
+        <v>-574.16</v>
       </c>
       <c r="D195" t="s">
         <v>64</v>
@@ -3310,7 +3310,7 @@
         <v>57</v>
       </c>
       <c r="C196">
-        <v>33.24</v>
+        <v>-33.24</v>
       </c>
       <c r="D196" t="s">
         <v>62</v>
@@ -3324,7 +3324,7 @@
         <v>40</v>
       </c>
       <c r="C197">
-        <v>30.47</v>
+        <v>-30.47</v>
       </c>
       <c r="D197" t="s">
         <v>60</v>
@@ -3338,7 +3338,7 @@
         <v>57</v>
       </c>
       <c r="C198">
-        <v>2.41</v>
+        <v>-2.41</v>
       </c>
       <c r="D198" t="s">
         <v>62</v>
@@ -3352,7 +3352,7 @@
         <v>52</v>
       </c>
       <c r="C199">
-        <v>416.66</v>
+        <v>-416.66</v>
       </c>
       <c r="D199" t="s">
         <v>59</v>
@@ -3366,7 +3366,7 @@
         <v>53</v>
       </c>
       <c r="C200">
-        <v>82.29000000000001</v>
+        <v>-82.29000000000001</v>
       </c>
       <c r="D200" t="s">
         <v>64</v>
@@ -3380,7 +3380,7 @@
         <v>55</v>
       </c>
       <c r="C201">
-        <v>38.22</v>
+        <v>-38.22</v>
       </c>
       <c r="D201" t="s">
         <v>62</v>
